--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_tarapaca.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.77856797428385</v>
+      </c>
+      <c r="C2">
         <v>26.35123602537479</v>
-      </c>
-      <c r="C2">
-        <v>27.77856797428385</v>
       </c>
       <c r="D2">
         <v>3.794888403098265</v>
       </c>
       <c r="E2">
-        <v>17.09678163571346</v>
+        <v>18.02284000461414</v>
       </c>
       <c r="F2">
         <v>64.88037835967239</v>
       </c>
       <c r="G2">
-        <v>18.02284000461414</v>
+        <v>17.09678163571346</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>37.68204597322542</v>
+      </c>
+      <c r="C3">
         <v>14.8166011810931</v>
-      </c>
-      <c r="C3">
-        <v>37.68204597322542</v>
       </c>
       <c r="D3">
         <v>6.749186184994045</v>
       </c>
       <c r="E3">
-        <v>9.715890243996514</v>
+        <v>24.7097575463038</v>
       </c>
       <c r="F3">
         <v>65.5743522096997</v>
       </c>
       <c r="G3">
-        <v>24.7097575463038</v>
+        <v>9.715890243996514</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>35.70502291000259</v>
+      </c>
+      <c r="C4">
         <v>22.25296100976917</v>
-      </c>
-      <c r="C4">
-        <v>35.70502291000259</v>
       </c>
       <c r="D4">
         <v>4.493783993783993</v>
       </c>
       <c r="E4">
-        <v>14.08789885611078</v>
+        <v>22.60412675825078</v>
       </c>
       <c r="F4">
         <v>63.30797438563845</v>
       </c>
       <c r="G4">
-        <v>22.60412675825078</v>
+        <v>14.08789885611078</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>45.17611026033691</v>
+      </c>
+      <c r="C5">
         <v>41.80704441041348</v>
-      </c>
-      <c r="C5">
-        <v>45.17611026033691</v>
       </c>
       <c r="D5">
         <v>2.391941391941392</v>
       </c>
       <c r="E5">
-        <v>22.35872235872236</v>
+        <v>24.16052416052416</v>
       </c>
       <c r="F5">
         <v>53.48075348075348</v>
       </c>
       <c r="G5">
-        <v>24.16052416052416</v>
+        <v>22.35872235872236</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>35.37964458804523</v>
+      </c>
+      <c r="C6">
         <v>28.59450726978998</v>
-      </c>
-      <c r="C6">
-        <v>35.37964458804523</v>
       </c>
       <c r="D6">
         <v>3.497175141242938</v>
       </c>
       <c r="E6">
-        <v>17.4384236453202</v>
+        <v>21.57635467980295</v>
       </c>
       <c r="F6">
         <v>60.98522167487685</v>
       </c>
       <c r="G6">
-        <v>21.57635467980295</v>
+        <v>17.4384236453202</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>46.77887405687754</v>
+      </c>
+      <c r="C7">
         <v>31.51479976784678</v>
-      </c>
-      <c r="C7">
-        <v>46.77887405687754</v>
       </c>
       <c r="D7">
         <v>3.173112338858195</v>
       </c>
       <c r="E7">
+        <v>26.23697916666666</v>
+      </c>
+      <c r="F7">
+        <v>56.08723958333333</v>
+      </c>
+      <c r="G7">
         <v>17.67578125</v>
-      </c>
-      <c r="F7">
-        <v>56.08723958333334</v>
-      </c>
-      <c r="G7">
-        <v>26.23697916666667</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>39.07369498464688</v>
+      </c>
+      <c r="C8">
         <v>35.28659160696008</v>
-      </c>
-      <c r="C8">
-        <v>39.07369498464688</v>
       </c>
       <c r="D8">
         <v>2.833937635968093</v>
       </c>
       <c r="E8">
-        <v>20.23774581743469</v>
+        <v>22.40974464338127</v>
       </c>
       <c r="F8">
         <v>57.35250953918403</v>
       </c>
       <c r="G8">
-        <v>22.40974464338127</v>
+        <v>20.23774581743469</v>
       </c>
     </row>
   </sheetData>
